--- a/astro-site/public/dl/chocolate-shop-checklist-templates/BONUS-02-chocolate-shop-holiday-calendar.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/BONUS-02-chocolate-shop-holiday-calendar.xlsx
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>▸ Adjust the dates to your area and market. UK: Mothering Sunday (March), bank holidays and Boxing Day.</t>
+          <t>▸ Adjust the dates to your area and market. UK: Mothering Sunday (3 weeks before Easter: March or early April), bank holidays and Boxing Day.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>St. Patrick's Day (17) · Easter prep (date varies) · kids' spring break workshops</t>
+          <t>St. Patrick's Day (17) · Easter prep (Easter itself falls in March some years: 2027, March 28) · kids' spring break workshops</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Easter (date varies): eggs, bunnies and baskets · graduation season starts (Apr–Jun): custom boxes and figures</t>
+          <t>Easter (date varies): eggs, bunnies and baskets · graduation and spring wedding orders open (ceremonies May–June): favors and custom boxes</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Mother's Day (2nd Sunday): premium gift boxes, pre-orders closed 2 weeks out · Teacher Appreciation Week · graduation peak</t>
+          <t>Mother's Day (2nd Sunday): premium gift boxes, pre-orders open 2–3 weeks out, order deadline a few days before · Teacher Appreciation Week · graduation peak</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Halloween (31): seasonal figures and bonbons · Sweetest Day · National Chocolate Day (28) · holiday production ramps up · publish the holiday catalog</t>
+          <t>Sweetest Day (3rd Saturday, mainly Midwest) · National Chocolate Day (28) · Halloween (31): seasonal figures and bonbons · holiday production ramps up · publish the holiday catalog</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
